--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.08903983640811</v>
+        <v>9.439468973416318</v>
       </c>
       <c r="D2" t="n">
-        <v>46.01465839127319</v>
+        <v>7.477381988581894</v>
       </c>
       <c r="E2" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F2" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.05914266410202</v>
+        <v>2.447110682916579</v>
       </c>
       <c r="D3" t="n">
-        <v>9.370832406995657</v>
+        <v>1.522760266136794</v>
       </c>
       <c r="E3" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F3" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.96372641063206</v>
+        <v>4.38160554172771</v>
       </c>
       <c r="D4" t="n">
-        <v>20.39214839777601</v>
+        <v>3.313724114638602</v>
       </c>
       <c r="E4" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F4" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.96347686658191</v>
+        <v>6.819064990819562</v>
       </c>
       <c r="D5" t="n">
-        <v>40.69683867697866</v>
+        <v>6.613236285009033</v>
       </c>
       <c r="E5" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F5" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.00619224140706</v>
+        <v>5.363506239228647</v>
       </c>
       <c r="D6" t="n">
-        <v>31.82439524984058</v>
+        <v>5.171464228099094</v>
       </c>
       <c r="E6" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F6" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7.677051301354014</v>
+        <v>1.247520836470027</v>
       </c>
       <c r="D7" t="n">
-        <v>4.356292392742544</v>
+        <v>0.7078975138206635</v>
       </c>
       <c r="E7" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F7" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.37536363784473</v>
+        <v>8.510996591149768</v>
       </c>
       <c r="D8" t="n">
-        <v>51.52118837834877</v>
+        <v>8.372193111481677</v>
       </c>
       <c r="E8" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F8" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.96469526422533</v>
+        <v>6.169262980436617</v>
       </c>
       <c r="D9" t="n">
-        <v>37.64740818668242</v>
+        <v>6.117703830335893</v>
       </c>
       <c r="E9" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F9" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.15725071217692</v>
+        <v>6.850553240728749</v>
       </c>
       <c r="D10" t="n">
-        <v>42.19021807917989</v>
+        <v>6.855910437866732</v>
       </c>
       <c r="E10" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F10" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>59.76182991955221</v>
+        <v>9.711297361927233</v>
       </c>
       <c r="D11" t="n">
-        <v>59.37811341052499</v>
+        <v>9.648943429210311</v>
       </c>
       <c r="E11" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F11" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>64.09058130469587</v>
+        <v>10.41471946201308</v>
       </c>
       <c r="D12" t="n">
-        <v>63.59441351013152</v>
+        <v>10.33409219539637</v>
       </c>
       <c r="E12" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F12" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.57160448582287</v>
+        <v>6.267885728946217</v>
       </c>
       <c r="D13" t="n">
-        <v>41.53082502526811</v>
+        <v>6.748759066606069</v>
       </c>
       <c r="E13" t="n">
-        <v>16.71119726986413</v>
+        <v>2.715569556352922</v>
       </c>
       <c r="F13" t="n">
-        <v>17.53951230737063</v>
+        <v>2.850170749947727</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
